--- a/grupos/5AEV - Estadisticos 20221.xlsx
+++ b/grupos/5AEV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="129">
   <si>
     <t>Materia</t>
   </si>
@@ -164,15 +164,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
@@ -197,214 +197,214 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ZGAIP</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>JOAQUIN</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>NORKYS AIRY</t>
+  </si>
+  <si>
+    <t>JORGE HUMBERTO</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>CRISTIAN JAHIR</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>DIEGO IVAN</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>JOHAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>JORGE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
     <t>AVENDAÑO</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
     <t>CANUTO</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
     <t>ROSETE</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ZGAIP</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>MEDINA</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>JOAQUIN</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
     <t>SALAS</t>
   </si>
   <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
     <t>AXEL JESUS</t>
   </si>
   <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
     <t>ISRAEL</t>
   </si>
   <si>
     <t>KARLA JOVANA</t>
   </si>
   <si>
-    <t>NORKYS AIRY</t>
-  </si>
-  <si>
-    <t>JORGE HUMBERTO</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
     <t>MIGUEL ANGEL</t>
   </si>
   <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAHIR</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>DIEGO IVAN</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>JOHAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
     <t>AMANDA MICHEL</t>
   </si>
   <si>
     <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>JORGE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ALDIR ADALBERTO</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>YAEL</t>
   </si>
 </sst>
 </file>
@@ -921,7 +921,7 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H4">
         <v>7</v>
@@ -984,7 +984,7 @@
         <v>9</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC4">
         <v>7</v>
@@ -1010,7 +1010,7 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -1073,7 +1073,7 @@
         <v>9</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC5">
         <v>5</v>
@@ -1099,7 +1099,7 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H6">
         <v>7</v>
@@ -1162,7 +1162,7 @@
         <v>10</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC6">
         <v>7</v>
@@ -1188,7 +1188,7 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H7">
         <v>10</v>
@@ -1251,7 +1251,7 @@
         <v>10</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC7">
         <v>10</v>
@@ -1262,7 +1262,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -1325,7 +1325,7 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X8">
         <v>5</v>
@@ -1440,7 +1440,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>7</v>
@@ -1503,7 +1503,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1633,7 +1633,7 @@
         <v>9</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H12">
         <v>7</v>
@@ -1696,7 +1696,7 @@
         <v>9</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC12">
         <v>7</v>
@@ -1722,7 +1722,7 @@
         <v>6</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H13">
         <v>8</v>
@@ -1785,7 +1785,7 @@
         <v>6</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC13">
         <v>8</v>
@@ -1811,7 +1811,7 @@
         <v>10</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H14">
         <v>7</v>
@@ -1874,7 +1874,7 @@
         <v>10</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC14">
         <v>7</v>
@@ -1989,7 +1989,7 @@
         <v>6</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
         <v>5</v>
@@ -2052,7 +2052,7 @@
         <v>6</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC16">
         <v>5</v>
@@ -2078,7 +2078,7 @@
         <v>-1</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H17">
         <v>7</v>
@@ -2141,7 +2141,7 @@
         <v>-1</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC17">
         <v>7</v>
@@ -2256,7 +2256,7 @@
         <v>6</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H19">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>6</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC19">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>-1</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>5</v>
@@ -2408,7 +2408,7 @@
         <v>-1</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC20">
         <v>5</v>
@@ -2434,7 +2434,7 @@
         <v>-1</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H21">
         <v>5</v>
@@ -2497,7 +2497,7 @@
         <v>-1</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>5</v>
@@ -2523,7 +2523,7 @@
         <v>9</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H22">
         <v>8</v>
@@ -2586,7 +2586,7 @@
         <v>9</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC22">
         <v>8</v>
@@ -2612,7 +2612,7 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H23">
         <v>10</v>
@@ -2675,7 +2675,7 @@
         <v>10</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC23">
         <v>10</v>
@@ -2701,7 +2701,7 @@
         <v>10</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H24">
         <v>7</v>
@@ -2764,7 +2764,7 @@
         <v>10</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC24">
         <v>7</v>
@@ -2775,7 +2775,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C25">
         <v>5</v>
@@ -2838,7 +2838,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>5</v>
@@ -2864,7 +2864,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C26">
         <v>6</v>
@@ -2927,7 +2927,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>6</v>
@@ -2968,7 +2968,7 @@
         <v>6</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H27">
         <v>8</v>
@@ -3031,7 +3031,7 @@
         <v>6</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC27">
         <v>8</v>
@@ -3146,7 +3146,7 @@
         <v>6</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H29">
         <v>5</v>
@@ -3209,7 +3209,7 @@
         <v>6</v>
       </c>
       <c r="AB29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC29">
         <v>5</v>
@@ -3268,7 +3268,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>48</v>
@@ -3277,27 +3277,30 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26.92</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>7.1</v>
+      </c>
       <c r="I2">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>73.08</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -3306,30 +3309,30 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E3">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>57.69</v>
+      </c>
+      <c r="G3">
+        <v>42.31</v>
+      </c>
+      <c r="H3">
+        <v>6.7</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>26.92</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>7.1</v>
-      </c>
-      <c r="I3">
-        <v>19</v>
-      </c>
-      <c r="J3">
-        <v>73.08</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -3338,25 +3341,25 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>57.69</v>
+        <v>65.38</v>
       </c>
       <c r="G4">
-        <v>42.31</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3466,25 +3469,25 @@
         <v>26</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>96.15000000000001</v>
+      </c>
+      <c r="G8">
+        <v>3.85</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
+      </c>
+      <c r="I8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>84.62</v>
-      </c>
-      <c r="G8">
+      <c r="J8">
         <v>0</v>
-      </c>
-      <c r="H8">
-        <v>8.4</v>
-      </c>
-      <c r="I8">
-        <v>4</v>
-      </c>
-      <c r="J8">
-        <v>15.38</v>
       </c>
     </row>
   </sheetData>
@@ -3494,7 +3497,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3523,19 +3526,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920041</v>
+        <v>20330051920071</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>48</v>
@@ -3543,99 +3546,99 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920071</v>
+        <v>20330051920074</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920071</v>
+        <v>20330051920074</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920073</v>
+        <v>20330051920074</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920359</v>
+        <v>20330051920075</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920074</v>
+        <v>20330051920075</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
         <v>48</v>
@@ -3643,199 +3646,199 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920074</v>
+        <v>20330051920075</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920074</v>
+        <v>19330051920051</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920074</v>
+        <v>19330051920051</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920075</v>
+        <v>20330051920077</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920075</v>
+        <v>20330051920080</v>
       </c>
       <c r="B12" t="s">
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920075</v>
+        <v>20330051920081</v>
       </c>
       <c r="B13" t="s">
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920051</v>
+        <v>20330051920082</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920051</v>
+        <v>20330051920082</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920051</v>
+        <v>20330051920087</v>
       </c>
       <c r="B16" t="s">
         <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920077</v>
+        <v>20330051920090</v>
       </c>
       <c r="B17" t="s">
         <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
         <v>48</v>
@@ -3843,79 +3846,79 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>18330051920156</v>
+        <v>20330051920090</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920080</v>
+        <v>20330051920091</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920080</v>
+        <v>20330051920091</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920081</v>
+        <v>20330051920093</v>
       </c>
       <c r="B21" t="s">
         <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
         <v>48</v>
@@ -3923,156 +3926,156 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920081</v>
+        <v>20330051920059</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920082</v>
+        <v>20330051920059</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920082</v>
+        <v>20330051920061</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920087</v>
+        <v>20330051920061</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920087</v>
+        <v>20330051920064</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920090</v>
+        <v>20330051920065</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D27" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920090</v>
+        <v>20330051920065</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920090</v>
+        <v>20330051920065</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -4083,136 +4086,136 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>20330051920091</v>
+        <v>20330051920066</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>20330051920091</v>
+        <v>20330051920066</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920093</v>
+        <v>20330051920066</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>20330051920093</v>
+        <v>20330051920068</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="D33" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>20330051920059</v>
+        <v>20330051920070</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D34" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920059</v>
+        <v>20330051920070</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D35" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>20330051920059</v>
+        <v>20330051920070</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D36" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
@@ -4223,442 +4226,22 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>20330051920061</v>
+        <v>20330051920386</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C37" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D37" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F37" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920061</v>
-      </c>
-      <c r="B38" t="s">
-        <v>74</v>
-      </c>
-      <c r="C38" t="s">
-        <v>96</v>
-      </c>
-      <c r="D38" t="s">
-        <v>120</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920061</v>
-      </c>
-      <c r="B39" t="s">
-        <v>74</v>
-      </c>
-      <c r="C39" t="s">
-        <v>96</v>
-      </c>
-      <c r="D39" t="s">
-        <v>120</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920062</v>
-      </c>
-      <c r="B40" t="s">
-        <v>75</v>
-      </c>
-      <c r="C40" t="s">
-        <v>73</v>
-      </c>
-      <c r="D40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920063</v>
-      </c>
-      <c r="B41" t="s">
-        <v>76</v>
-      </c>
-      <c r="C41" t="s">
-        <v>97</v>
-      </c>
-      <c r="D41" t="s">
-        <v>122</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920064</v>
-      </c>
-      <c r="B42" t="s">
-        <v>77</v>
-      </c>
-      <c r="C42" t="s">
-        <v>98</v>
-      </c>
-      <c r="D42" t="s">
-        <v>123</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920064</v>
-      </c>
-      <c r="B43" t="s">
-        <v>77</v>
-      </c>
-      <c r="C43" t="s">
-        <v>98</v>
-      </c>
-      <c r="D43" t="s">
-        <v>123</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920065</v>
-      </c>
-      <c r="B44" t="s">
-        <v>78</v>
-      </c>
-      <c r="C44" t="s">
-        <v>99</v>
-      </c>
-      <c r="D44" t="s">
-        <v>124</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>20330051920065</v>
-      </c>
-      <c r="B45" t="s">
-        <v>78</v>
-      </c>
-      <c r="C45" t="s">
-        <v>99</v>
-      </c>
-      <c r="D45" t="s">
-        <v>124</v>
-      </c>
-      <c r="E45" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>20330051920065</v>
-      </c>
-      <c r="B46" t="s">
-        <v>78</v>
-      </c>
-      <c r="C46" t="s">
-        <v>99</v>
-      </c>
-      <c r="D46" t="s">
-        <v>124</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>20330051920065</v>
-      </c>
-      <c r="B47" t="s">
-        <v>78</v>
-      </c>
-      <c r="C47" t="s">
-        <v>99</v>
-      </c>
-      <c r="D47" t="s">
-        <v>124</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>20330051920066</v>
-      </c>
-      <c r="B48" t="s">
-        <v>79</v>
-      </c>
-      <c r="C48" t="s">
-        <v>100</v>
-      </c>
-      <c r="D48" t="s">
-        <v>125</v>
-      </c>
-      <c r="E48" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920066</v>
-      </c>
-      <c r="B49" t="s">
-        <v>79</v>
-      </c>
-      <c r="C49" t="s">
-        <v>100</v>
-      </c>
-      <c r="D49" t="s">
-        <v>125</v>
-      </c>
-      <c r="E49" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920066</v>
-      </c>
-      <c r="B50" t="s">
-        <v>79</v>
-      </c>
-      <c r="C50" t="s">
-        <v>100</v>
-      </c>
-      <c r="D50" t="s">
-        <v>125</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920066</v>
-      </c>
-      <c r="B51" t="s">
-        <v>79</v>
-      </c>
-      <c r="C51" t="s">
-        <v>100</v>
-      </c>
-      <c r="D51" t="s">
-        <v>125</v>
-      </c>
-      <c r="E51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>20330051920068</v>
-      </c>
-      <c r="B52" t="s">
-        <v>80</v>
-      </c>
-      <c r="C52" t="s">
-        <v>68</v>
-      </c>
-      <c r="D52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>20330051920068</v>
-      </c>
-      <c r="B53" t="s">
-        <v>80</v>
-      </c>
-      <c r="C53" t="s">
-        <v>68</v>
-      </c>
-      <c r="D53" t="s">
-        <v>126</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>20330051920070</v>
-      </c>
-      <c r="B54" t="s">
-        <v>80</v>
-      </c>
-      <c r="C54" t="s">
-        <v>101</v>
-      </c>
-      <c r="D54" t="s">
-        <v>127</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>20330051920070</v>
-      </c>
-      <c r="B55" t="s">
-        <v>80</v>
-      </c>
-      <c r="C55" t="s">
-        <v>101</v>
-      </c>
-      <c r="D55" t="s">
-        <v>127</v>
-      </c>
-      <c r="E55" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>20330051920070</v>
-      </c>
-      <c r="B56" t="s">
-        <v>80</v>
-      </c>
-      <c r="C56" t="s">
-        <v>101</v>
-      </c>
-      <c r="D56" t="s">
-        <v>127</v>
-      </c>
-      <c r="E56" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>20330051920386</v>
-      </c>
-      <c r="B57" t="s">
-        <v>81</v>
-      </c>
-      <c r="C57" t="s">
-        <v>102</v>
-      </c>
-      <c r="D57" t="s">
-        <v>128</v>
-      </c>
-      <c r="E57" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>20330051920386</v>
-      </c>
-      <c r="B58" t="s">
-        <v>81</v>
-      </c>
-      <c r="C58" t="s">
-        <v>102</v>
-      </c>
-      <c r="D58" t="s">
-        <v>128</v>
-      </c>
-      <c r="E58" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -4697,64 +4280,64 @@
         <v>20330051920074</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920065</v>
+        <v>20330051920075</v>
       </c>
       <c r="B3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" t="s">
         <v>78</v>
       </c>
-      <c r="C3" t="s">
-        <v>99</v>
-      </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920066</v>
+        <v>20330051920065</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920075</v>
+        <v>20330051920066</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -4762,16 +4345,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920051</v>
+        <v>20330051920070</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -4779,84 +4362,84 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920090</v>
+        <v>19330051920051</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920059</v>
+        <v>20330051920082</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920061</v>
+        <v>20330051920090</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920070</v>
+        <v>20330051920091</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920071</v>
+        <v>20330051920059</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -4864,16 +4447,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920080</v>
+        <v>20330051920061</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -4881,152 +4464,152 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920081</v>
+        <v>20330051920071</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920082</v>
+        <v>20330051920077</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920087</v>
+        <v>20330051920080</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920091</v>
+        <v>20330051920081</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920093</v>
+        <v>20330051920087</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920064</v>
+        <v>20330051920093</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920068</v>
+        <v>20330051920064</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920386</v>
+        <v>20330051920068</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920041</v>
+        <v>20330051920386</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -5034,53 +4617,53 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920073</v>
+        <v>20330051920041</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920359</v>
+        <v>20330051920073</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920077</v>
+        <v>20330051920359</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="C24" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -5088,16 +4671,16 @@
         <v>18330051920156</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -5105,16 +4688,16 @@
         <v>20330051920062</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -5122,16 +4705,16 @@
         <v>20330051920063</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5141,7 +4724,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5173,22 +4756,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920080</v>
+        <v>19330051920051</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -5196,22 +4779,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920080</v>
+        <v>19330051920051</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -5219,22 +4802,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920081</v>
+        <v>20330051920082</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -5242,22 +4825,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920081</v>
+        <v>20330051920082</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -5265,22 +4848,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920082</v>
+        <v>20330051920091</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -5288,22 +4871,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920082</v>
+        <v>20330051920091</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -5311,42 +4894,42 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920091</v>
+        <v>20330051920093</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
         <v>49</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920091</v>
+        <v>20330051920093</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
         <v>48</v>
@@ -5357,22 +4940,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920064</v>
+        <v>20330051920080</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -5380,19 +4963,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920064</v>
+        <v>20330051920081</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
         <v>48</v>
@@ -5403,22 +4986,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920068</v>
+        <v>20330051920064</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -5429,159 +5012,21 @@
         <v>20330051920068</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
         <v>48</v>
       </c>
       <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920041</v>
-      </c>
-      <c r="B14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920073</v>
-      </c>
-      <c r="B15" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920359</v>
-      </c>
-      <c r="B16" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>18330051920156</v>
-      </c>
-      <c r="B17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" t="s">
-        <v>111</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920062</v>
-      </c>
-      <c r="B18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" t="s">
-        <v>121</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>48</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920063</v>
-      </c>
-      <c r="B19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" t="s">
-        <v>122</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>48</v>
-      </c>
-      <c r="G19">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/5AEV - Estadisticos 20221.xlsx
+++ b/grupos/5AEV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="129">
   <si>
     <t>Materia</t>
   </si>
@@ -173,13 +173,13 @@
     <t>González Nuñez Veronica</t>
   </si>
   <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
     <t>Molina Quezada Raúl</t>
@@ -927,25 +927,25 @@
         <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -981,13 +981,13 @@
         <v>6</v>
       </c>
       <c r="AA4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB4">
         <v>10</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1016,25 +1016,25 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1064,19 +1064,19 @@
         <v>6</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z5">
         <v>-1</v>
       </c>
       <c r="AA5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB5">
         <v>7</v>
       </c>
       <c r="AC5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1105,25 +1105,25 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1153,19 +1153,19 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z6">
         <v>6</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>6</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1194,25 +1194,25 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1274,7 +1274,7 @@
         <v>-1</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -1283,25 +1283,25 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1337,7 +1337,7 @@
         <v>-1</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB8">
         <v>-1</v>
@@ -1363,7 +1363,7 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -1372,25 +1372,25 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1414,19 +1414,19 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z9">
         <v>-1</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB9">
         <v>-1</v>
@@ -1461,25 +1461,25 @@
         <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1509,19 +1509,19 @@
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>-1</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB10">
         <v>-1</v>
       </c>
       <c r="AC10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1550,25 +1550,25 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1639,25 +1639,25 @@
         <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1693,13 +1693,13 @@
         <v>7</v>
       </c>
       <c r="AA12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB12">
         <v>10</v>
       </c>
       <c r="AC12">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1728,25 +1728,25 @@
         <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1770,7 +1770,7 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -1782,7 +1782,7 @@
         <v>-1</v>
       </c>
       <c r="AA13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB13">
         <v>6</v>
@@ -1817,25 +1817,25 @@
         <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1859,13 +1859,13 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z14">
         <v>-1</v>
@@ -1877,7 +1877,7 @@
         <v>8</v>
       </c>
       <c r="AC14">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1906,25 +1906,25 @@
         <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1948,13 +1948,13 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z15">
         <v>-1</v>
@@ -1966,7 +1966,7 @@
         <v>-1</v>
       </c>
       <c r="AC15">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1995,25 +1995,25 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2043,19 +2043,19 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z16">
         <v>-1</v>
       </c>
       <c r="AA16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB16">
         <v>6</v>
       </c>
       <c r="AC16">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2075,7 +2075,7 @@
         <v>-1</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G17">
         <v>6</v>
@@ -2084,25 +2084,25 @@
         <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2126,7 +2126,7 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -2138,13 +2138,13 @@
         <v>-1</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB17">
         <v>6</v>
       </c>
       <c r="AC17">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2173,25 +2173,25 @@
         <v>7</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2215,19 +2215,19 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z18">
         <v>-1</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB18">
         <v>-1</v>
@@ -2262,25 +2262,25 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2304,25 +2304,25 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X19">
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z19">
         <v>-1</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB19">
         <v>9</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2342,7 +2342,7 @@
         <v>-1</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G20">
         <v>6</v>
@@ -2351,25 +2351,25 @@
         <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2405,13 +2405,13 @@
         <v>-1</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB20">
         <v>6</v>
       </c>
       <c r="AC20">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2431,7 +2431,7 @@
         <v>-1</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G21">
         <v>8</v>
@@ -2440,25 +2440,25 @@
         <v>5</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2482,7 +2482,7 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2494,13 +2494,13 @@
         <v>-1</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB21">
         <v>8</v>
       </c>
       <c r="AC21">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2529,25 +2529,25 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2571,7 +2571,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2583,13 +2583,13 @@
         <v>-1</v>
       </c>
       <c r="AA22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB22">
         <v>10</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2618,25 +2618,25 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2707,25 +2707,25 @@
         <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2755,19 +2755,19 @@
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z24">
         <v>7</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB24">
         <v>6</v>
       </c>
       <c r="AC24">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2787,7 +2787,7 @@
         <v>-1</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G25">
         <v>-1</v>
@@ -2796,25 +2796,25 @@
         <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2850,13 +2850,13 @@
         <v>-1</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB25">
         <v>-1</v>
       </c>
       <c r="AC25">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2876,7 +2876,7 @@
         <v>-1</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G26">
         <v>-1</v>
@@ -2885,25 +2885,25 @@
         <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2939,7 +2939,7 @@
         <v>-1</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB26">
         <v>-1</v>
@@ -2974,25 +2974,25 @@
         <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3028,7 +3028,7 @@
         <v>-1</v>
       </c>
       <c r="AA27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB27">
         <v>9</v>
@@ -3054,7 +3054,7 @@
         <v>-1</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G28">
         <v>-1</v>
@@ -3063,25 +3063,25 @@
         <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3117,13 +3117,13 @@
         <v>-1</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB28">
         <v>-1</v>
       </c>
       <c r="AC28">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3152,25 +3152,25 @@
         <v>5</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3194,7 +3194,7 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>6</v>
@@ -3206,7 +3206,7 @@
         <v>-1</v>
       </c>
       <c r="AA29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB29">
         <v>8</v>
@@ -3309,16 +3309,16 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>57.69</v>
+        <v>61.54</v>
       </c>
       <c r="G3">
-        <v>42.31</v>
+        <v>38.46</v>
       </c>
       <c r="H3">
         <v>6.7</v>
@@ -3364,7 +3364,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
@@ -3385,7 +3385,7 @@
         <v>34.62</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
@@ -3405,30 +3405,30 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>80.77</v>
+      </c>
+      <c r="G6">
+        <v>19.23</v>
+      </c>
+      <c r="H6">
+        <v>6.7</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>69.23</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>7.9</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>30.77</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
@@ -3437,19 +3437,19 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>80.77</v>
+        <v>84.62</v>
       </c>
       <c r="G7">
-        <v>19.23</v>
+        <v>15.38</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3481,7 +3481,7 @@
         <v>3.85</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -3497,7 +3497,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3586,22 +3586,22 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920074</v>
+        <v>20330051920075</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3618,64 +3618,64 @@
         <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920075</v>
+        <v>19330051920051</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920075</v>
+        <v>19330051920051</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920051</v>
+        <v>20330051920077</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -3686,16 +3686,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920051</v>
+        <v>20330051920080</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -3706,56 +3706,56 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920077</v>
+        <v>20330051920081</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920080</v>
+        <v>20330051920082</v>
       </c>
       <c r="B12" t="s">
         <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920081</v>
+        <v>20330051920082</v>
       </c>
       <c r="B13" t="s">
         <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -3766,36 +3766,36 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920082</v>
+        <v>20330051920087</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920082</v>
+        <v>20330051920090</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -3806,36 +3806,36 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920087</v>
+        <v>20330051920091</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920090</v>
+        <v>20330051920091</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -3846,56 +3846,56 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920090</v>
+        <v>20330051920093</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920091</v>
+        <v>20330051920059</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920091</v>
+        <v>20330051920061</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -3906,16 +3906,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920093</v>
+        <v>20330051920064</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -3926,96 +3926,96 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920059</v>
+        <v>20330051920065</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920059</v>
+        <v>20330051920065</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920061</v>
+        <v>20330051920066</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920061</v>
+        <v>20330051920066</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920064</v>
+        <v>20330051920068</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="D26" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -4026,16 +4026,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920065</v>
+        <v>20330051920070</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -4046,16 +4046,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920065</v>
+        <v>20330051920070</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D28" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -4066,181 +4066,21 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920065</v>
+        <v>20330051920386</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920066</v>
-      </c>
-      <c r="B30" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30" t="s">
-        <v>111</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920066</v>
-      </c>
-      <c r="B31" t="s">
-        <v>73</v>
-      </c>
-      <c r="C31" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31" t="s">
-        <v>111</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920066</v>
-      </c>
-      <c r="B32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" t="s">
-        <v>92</v>
-      </c>
-      <c r="D32" t="s">
-        <v>111</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920068</v>
-      </c>
-      <c r="B33" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" t="s">
-        <v>112</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920070</v>
-      </c>
-      <c r="B34" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" t="s">
-        <v>93</v>
-      </c>
-      <c r="D34" t="s">
-        <v>113</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920070</v>
-      </c>
-      <c r="B35" t="s">
-        <v>74</v>
-      </c>
-      <c r="C35" t="s">
-        <v>93</v>
-      </c>
-      <c r="D35" t="s">
-        <v>113</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920070</v>
-      </c>
-      <c r="B36" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" t="s">
-        <v>93</v>
-      </c>
-      <c r="D36" t="s">
-        <v>113</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920386</v>
-      </c>
-      <c r="B37" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" t="s">
-        <v>94</v>
-      </c>
-      <c r="D37" t="s">
-        <v>114</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
         <v>48</v>
       </c>
     </row>
@@ -4289,7 +4129,7 @@
         <v>96</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4306,72 +4146,72 @@
         <v>97</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920065</v>
+        <v>19330051920051</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920066</v>
+        <v>20330051920082</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920070</v>
+        <v>20330051920091</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920051</v>
+        <v>20330051920065</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -4379,16 +4219,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920082</v>
+        <v>20330051920066</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -4396,16 +4236,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920090</v>
+        <v>20330051920070</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -4413,67 +4253,67 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920091</v>
+        <v>20330051920071</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920059</v>
+        <v>20330051920077</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920061</v>
+        <v>20330051920080</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920071</v>
+        <v>20330051920081</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -4481,16 +4321,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920077</v>
+        <v>20330051920087</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -4498,16 +4338,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920080</v>
+        <v>20330051920090</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -4515,16 +4355,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920081</v>
+        <v>20330051920093</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -4532,16 +4372,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920087</v>
+        <v>20330051920059</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -4549,16 +4389,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920093</v>
+        <v>20330051920061</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -4724,7 +4564,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4756,16 +4596,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920051</v>
+        <v>20330051920082</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4779,16 +4619,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920051</v>
+        <v>20330051920082</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4802,16 +4642,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920082</v>
+        <v>20330051920093</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4825,39 +4665,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920082</v>
+        <v>20330051920093</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920091</v>
+        <v>20330051920071</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4871,62 +4711,62 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920091</v>
+        <v>20330051920073</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920093</v>
+        <v>20330051920080</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920093</v>
+        <v>20330051920081</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4940,16 +4780,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920080</v>
+        <v>20330051920087</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4963,16 +4803,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920081</v>
+        <v>20330051920064</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4986,16 +4826,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920064</v>
+        <v>20330051920068</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -5004,29 +4844,6 @@
         <v>48</v>
       </c>
       <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920068</v>
-      </c>
-      <c r="B13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" t="s">
-        <v>112</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/5AEV - Estadisticos 20221.xlsx
+++ b/grupos/5AEV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="129">
   <si>
     <t>Materia</t>
   </si>
@@ -167,6 +167,9 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Silva Villegas Mario</t>
   </si>
   <si>
@@ -174,9 +177,6 @@
   </si>
   <si>
     <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
     <t>Zarate Amezcua Eladio Jorge</t>
@@ -930,7 +930,7 @@
         <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>9</v>
@@ -942,7 +942,7 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
         <v>10</v>
@@ -1019,7 +1019,7 @@
         <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
         <v>8</v>
@@ -1061,7 +1061,7 @@
         <v>10</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -1108,7 +1108,7 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>5</v>
@@ -1120,7 +1120,7 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>8</v>
@@ -1162,7 +1162,7 @@
         <v>8</v>
       </c>
       <c r="AB6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC6">
         <v>8</v>
@@ -1197,7 +1197,7 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>9</v>
@@ -1209,7 +1209,7 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
         <v>10</v>
@@ -1286,7 +1286,7 @@
         <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>5</v>
@@ -1375,7 +1375,7 @@
         <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <v>5</v>
@@ -1464,7 +1464,7 @@
         <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
         <v>7</v>
@@ -1553,7 +1553,7 @@
         <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>7</v>
@@ -1642,7 +1642,7 @@
         <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
         <v>8</v>
@@ -1654,7 +1654,7 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>10</v>
@@ -1696,7 +1696,7 @@
         <v>10</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC12">
         <v>9</v>
@@ -1731,7 +1731,7 @@
         <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>6</v>
@@ -1743,7 +1743,7 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
         <v>8</v>
@@ -1820,7 +1820,7 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
         <v>9</v>
@@ -1832,7 +1832,7 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>8</v>
@@ -1909,7 +1909,7 @@
         <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>5</v>
@@ -1998,7 +1998,7 @@
         <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>9</v>
@@ -2010,7 +2010,7 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>8</v>
@@ -2040,7 +2040,7 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -2087,7 +2087,7 @@
         <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>5</v>
@@ -2099,7 +2099,7 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>8</v>
@@ -2176,7 +2176,7 @@
         <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>5</v>
@@ -2218,7 +2218,7 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2265,7 +2265,7 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>7</v>
@@ -2277,7 +2277,7 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
         <v>9</v>
@@ -2307,7 +2307,7 @@
         <v>10</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2319,7 +2319,7 @@
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC19">
         <v>9</v>
@@ -2354,7 +2354,7 @@
         <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>5</v>
@@ -2396,7 +2396,7 @@
         <v>7</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2443,7 +2443,7 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>5</v>
@@ -2485,7 +2485,7 @@
         <v>10</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>5</v>
@@ -2532,7 +2532,7 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>8</v>
@@ -2544,7 +2544,7 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
         <v>9</v>
@@ -2621,7 +2621,7 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
         <v>10</v>
@@ -2633,7 +2633,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>10</v>
@@ -2710,7 +2710,7 @@
         <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
         <v>5</v>
@@ -2722,7 +2722,7 @@
         <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
         <v>8</v>
@@ -2799,7 +2799,7 @@
         <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>5</v>
@@ -2888,7 +2888,7 @@
         <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>5</v>
@@ -2930,7 +2930,7 @@
         <v>6</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2977,7 +2977,7 @@
         <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>8</v>
@@ -2989,7 +2989,7 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>7</v>
@@ -3031,7 +3031,7 @@
         <v>8</v>
       </c>
       <c r="AB27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC27">
         <v>8</v>
@@ -3066,7 +3066,7 @@
         <v>7</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
         <v>5</v>
@@ -3108,7 +3108,7 @@
         <v>7</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>5</v>
@@ -3155,7 +3155,7 @@
         <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
         <v>5</v>
@@ -3197,7 +3197,7 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y29">
         <v>5</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -3321,7 +3321,7 @@
         <v>38.46</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -3341,30 +3341,30 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>61.54</v>
+      </c>
+      <c r="G4">
+        <v>38.46</v>
+      </c>
+      <c r="H4">
+        <v>6.7</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>65.38</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>7.9</v>
-      </c>
-      <c r="I4">
-        <v>9</v>
-      </c>
-      <c r="J4">
-        <v>34.62</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
@@ -3376,27 +3376,27 @@
         <v>17</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>65.38</v>
       </c>
       <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>7.9</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
         <v>34.62</v>
-      </c>
-      <c r="H5">
-        <v>7.2</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
@@ -3405,19 +3405,19 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>80.77</v>
+        <v>65.38</v>
       </c>
       <c r="G6">
-        <v>19.23</v>
+        <v>34.62</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3561,7 +3561,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3601,7 +3601,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3641,7 +3641,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3681,7 +3681,7 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3741,7 +3741,7 @@
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3821,7 +3821,7 @@
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -3941,7 +3941,7 @@
         <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -3981,7 +3981,7 @@
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4041,7 +4041,7 @@
         <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -4564,7 +4564,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4634,7 +4634,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -4642,62 +4642,62 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920093</v>
+        <v>20330051920087</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920093</v>
+        <v>20330051920087</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920071</v>
+        <v>20330051920093</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4711,22 +4711,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920073</v>
+        <v>20330051920093</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4734,16 +4734,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920080</v>
+        <v>20330051920071</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4757,39 +4757,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920081</v>
+        <v>20330051920073</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920087</v>
+        <v>20330051920080</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4803,16 +4803,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920064</v>
+        <v>20330051920081</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4826,16 +4826,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920068</v>
+        <v>20330051920064</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4844,6 +4844,29 @@
         <v>48</v>
       </c>
       <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920068</v>
+      </c>
+      <c r="B13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/5AEV - Estadisticos 20221.xlsx
+++ b/grupos/5AEV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="129">
   <si>
     <t>Materia</t>
   </si>
@@ -936,7 +936,7 @@
         <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -978,7 +978,7 @@
         <v>9</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA4">
         <v>10</v>
@@ -1114,7 +1114,7 @@
         <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -1156,7 +1156,7 @@
         <v>5</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA6">
         <v>8</v>
@@ -1203,7 +1203,7 @@
         <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -1559,7 +1559,7 @@
         <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M11">
         <v>6</v>
@@ -1601,7 +1601,7 @@
         <v>7</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA11">
         <v>7</v>
@@ -1648,7 +1648,7 @@
         <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M12">
         <v>10</v>
@@ -1690,7 +1690,7 @@
         <v>8</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA12">
         <v>10</v>
@@ -2627,7 +2627,7 @@
         <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -2716,7 +2716,7 @@
         <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M24">
         <v>7</v>
@@ -2758,7 +2758,7 @@
         <v>7</v>
       </c>
       <c r="Z24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA24">
         <v>9</v>
@@ -3277,19 +3277,19 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>26.92</v>
+        <v>11.54</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>15.38</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
         <v>19</v>
@@ -4564,7 +4564,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4596,91 +4596,91 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920082</v>
+        <v>20330051920073</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920082</v>
+        <v>20330051920073</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920087</v>
+        <v>20330051920082</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920087</v>
+        <v>20330051920082</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -4688,62 +4688,62 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920093</v>
+        <v>20330051920087</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920093</v>
+        <v>20330051920087</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920071</v>
+        <v>20330051920093</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4757,22 +4757,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920073</v>
+        <v>20330051920093</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4780,16 +4780,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920080</v>
+        <v>20330051920071</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4803,16 +4803,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920081</v>
+        <v>18330051920156</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4821,21 +4821,21 @@
         <v>48</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920064</v>
+        <v>20330051920080</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4849,16 +4849,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920068</v>
+        <v>20330051920081</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4867,6 +4867,75 @@
         <v>48</v>
       </c>
       <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920063</v>
+      </c>
+      <c r="B14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920064</v>
+      </c>
+      <c r="B15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920068</v>
+      </c>
+      <c r="B16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/5AEV - Estadisticos 20221.xlsx
+++ b/grupos/5AEV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="129">
   <si>
     <t>Materia</t>
   </si>
@@ -197,9 +197,18 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>AVENDAÑO</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>CHAVEZ</t>
   </si>
   <si>
@@ -212,6 +221,9 @@
     <t>ESPINOZA</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -233,6 +245,12 @@
     <t>ROBLES</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
@@ -248,7 +266,10 @@
     <t>ZGAIP</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
   </si>
   <si>
     <t>RAMOS</t>
@@ -290,6 +311,9 @@
     <t>IXMATLAHUA</t>
   </si>
   <si>
+    <t>SALAS</t>
+  </si>
+  <si>
     <t>VELASCO</t>
   </si>
   <si>
@@ -305,9 +329,18 @@
     <t>OJEDA</t>
   </si>
   <si>
+    <t>AXEL JESUS</t>
+  </si>
+  <si>
     <t>MARCO ANTONIO</t>
   </si>
   <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>KARLA JOVANA</t>
+  </si>
+  <si>
     <t>NORKYS AIRY</t>
   </si>
   <si>
@@ -320,6 +353,9 @@
     <t>ADRIAN</t>
   </si>
   <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
     <t>LUIS ENRIQUE</t>
   </si>
   <si>
@@ -347,6 +383,12 @@
     <t>ALAN URIEL</t>
   </si>
   <si>
+    <t>AMANDA MICHEL</t>
+  </si>
+  <si>
+    <t>VICTOR GAEL</t>
+  </si>
+  <si>
     <t>JORGE ALEJANDRO</t>
   </si>
   <si>
@@ -363,48 +405,6 @@
   </si>
   <si>
     <t>YAEL</t>
-  </si>
-  <si>
-    <t>AVENDAÑO</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>AXEL JESUS</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>KARLA JOVANA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>AMANDA MICHEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
   </si>
 </sst>
 </file>
@@ -1004,7 +1004,7 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>9</v>
@@ -1025,13 +1025,13 @@
         <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M5">
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>7</v>
@@ -1067,7 +1067,7 @@
         <v>7</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA5">
         <v>7</v>
@@ -1271,13 +1271,13 @@
         <v>5</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F8">
         <v>5</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -1292,13 +1292,13 @@
         <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M8">
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -1334,13 +1334,13 @@
         <v>5</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA8">
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC8">
         <v>6</v>
@@ -1360,13 +1360,13 @@
         <v>9</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F9">
         <v>10</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H9">
         <v>5</v>
@@ -1381,13 +1381,13 @@
         <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M9">
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1423,13 +1423,13 @@
         <v>7</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA9">
         <v>8</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC9">
         <v>5</v>
@@ -1449,13 +1449,13 @@
         <v>6</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F10">
         <v>6</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>7</v>
@@ -1470,13 +1470,13 @@
         <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M10">
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
         <v>8</v>
@@ -1512,13 +1512,13 @@
         <v>7</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA10">
         <v>5</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -1544,7 +1544,7 @@
         <v>7</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H11">
         <v>5</v>
@@ -1565,7 +1565,7 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>6</v>
@@ -1607,7 +1607,7 @@
         <v>7</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC11">
         <v>5</v>
@@ -1716,7 +1716,7 @@
         <v>7</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F13">
         <v>6</v>
@@ -1737,7 +1737,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M13">
         <v>7</v>
@@ -1779,7 +1779,7 @@
         <v>7</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA13">
         <v>7</v>
@@ -1805,7 +1805,7 @@
         <v>8</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F14">
         <v>10</v>
@@ -1826,7 +1826,7 @@
         <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -1868,7 +1868,7 @@
         <v>9</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA14">
         <v>10</v>
@@ -1894,13 +1894,13 @@
         <v>8</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F15">
         <v>8</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H15">
         <v>6</v>
@@ -1915,13 +1915,13 @@
         <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M15">
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
         <v>8</v>
@@ -1957,13 +1957,13 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA15">
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC15">
         <v>7</v>
@@ -1983,7 +1983,7 @@
         <v>5</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F16">
         <v>6</v>
@@ -2004,7 +2004,7 @@
         <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>9</v>
@@ -2046,7 +2046,7 @@
         <v>7</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA16">
         <v>8</v>
@@ -2072,7 +2072,7 @@
         <v>5</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -2093,7 +2093,7 @@
         <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M17">
         <v>5</v>
@@ -2135,7 +2135,7 @@
         <v>5</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA17">
         <v>5</v>
@@ -2161,13 +2161,13 @@
         <v>6</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F18">
         <v>6</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H18">
         <v>7</v>
@@ -2182,13 +2182,13 @@
         <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M18">
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>7</v>
@@ -2224,13 +2224,13 @@
         <v>5</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA18">
         <v>7</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC18">
         <v>7</v>
@@ -2250,7 +2250,7 @@
         <v>5</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F19">
         <v>6</v>
@@ -2271,7 +2271,7 @@
         <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
         <v>5</v>
@@ -2313,7 +2313,7 @@
         <v>6</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA19">
         <v>5</v>
@@ -2339,7 +2339,7 @@
         <v>5</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F20">
         <v>6</v>
@@ -2360,13 +2360,13 @@
         <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M20">
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>8</v>
@@ -2402,13 +2402,13 @@
         <v>5</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA20">
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC20">
         <v>7</v>
@@ -2428,7 +2428,7 @@
         <v>5</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -2449,13 +2449,13 @@
         <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M21">
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
         <v>9</v>
@@ -2491,13 +2491,13 @@
         <v>5</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA21">
         <v>5</v>
       </c>
       <c r="AB21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC21">
         <v>7</v>
@@ -2517,7 +2517,7 @@
         <v>9</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F22">
         <v>9</v>
@@ -2538,7 +2538,7 @@
         <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -2580,7 +2580,7 @@
         <v>9</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -2784,13 +2784,13 @@
         <v>5</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F25">
         <v>6</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H25">
         <v>6</v>
@@ -2805,13 +2805,13 @@
         <v>5</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M25">
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
         <v>7</v>
@@ -2847,13 +2847,13 @@
         <v>5</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA25">
         <v>6</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC25">
         <v>7</v>
@@ -2873,13 +2873,13 @@
         <v>5</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F26">
         <v>6</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H26">
         <v>5</v>
@@ -2894,13 +2894,13 @@
         <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M26">
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>6</v>
@@ -2936,13 +2936,13 @@
         <v>5</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA26">
         <v>5</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC26">
         <v>5</v>
@@ -2962,7 +2962,7 @@
         <v>8</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F27">
         <v>6</v>
@@ -2983,7 +2983,7 @@
         <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>10</v>
@@ -3025,7 +3025,7 @@
         <v>8</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA27">
         <v>8</v>
@@ -3051,13 +3051,13 @@
         <v>5</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F28">
         <v>6</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H28">
         <v>5</v>
@@ -3072,13 +3072,13 @@
         <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M28">
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
         <v>8</v>
@@ -3114,13 +3114,13 @@
         <v>5</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA28">
         <v>5</v>
       </c>
       <c r="AB28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC28">
         <v>7</v>
@@ -3140,7 +3140,7 @@
         <v>5</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F29">
         <v>6</v>
@@ -3161,13 +3161,13 @@
         <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M29">
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
         <v>6</v>
@@ -3203,13 +3203,13 @@
         <v>5</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA29">
         <v>5</v>
       </c>
       <c r="AB29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC29">
         <v>5</v>
@@ -3277,25 +3277,25 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>11.54</v>
+        <v>30.77</v>
       </c>
       <c r="G2">
-        <v>15.38</v>
+        <v>69.23</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="I2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>73.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3376,22 +3376,22 @@
         <v>17</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F5">
         <v>65.38</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>34.62</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>34.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3497,7 +3497,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3522,566 +3522,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920071</v>
-      </c>
-      <c r="B2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920074</v>
-      </c>
-      <c r="B3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920074</v>
-      </c>
-      <c r="B4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920075</v>
-      </c>
-      <c r="B5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" t="s">
-        <v>97</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920075</v>
-      </c>
-      <c r="B6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920051</v>
-      </c>
-      <c r="B7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920051</v>
-      </c>
-      <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920077</v>
-      </c>
-      <c r="B9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" t="s">
-        <v>99</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920080</v>
-      </c>
-      <c r="B10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920081</v>
-      </c>
-      <c r="B11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920082</v>
-      </c>
-      <c r="B12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920082</v>
-      </c>
-      <c r="B13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920087</v>
-      </c>
-      <c r="B14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920090</v>
-      </c>
-      <c r="B15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" t="s">
-        <v>104</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920091</v>
-      </c>
-      <c r="B16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" t="s">
-        <v>105</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920091</v>
-      </c>
-      <c r="B17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" t="s">
-        <v>86</v>
-      </c>
-      <c r="D17" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920093</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920059</v>
-      </c>
-      <c r="B19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" t="s">
-        <v>88</v>
-      </c>
-      <c r="D19" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920061</v>
-      </c>
-      <c r="B20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" t="s">
-        <v>108</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920064</v>
-      </c>
-      <c r="B21" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" t="s">
-        <v>109</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920065</v>
-      </c>
-      <c r="B22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" t="s">
-        <v>91</v>
-      </c>
-      <c r="D22" t="s">
-        <v>110</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920065</v>
-      </c>
-      <c r="B23" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" t="s">
-        <v>110</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920066</v>
-      </c>
-      <c r="B24" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" t="s">
-        <v>111</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920066</v>
-      </c>
-      <c r="B25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" t="s">
-        <v>92</v>
-      </c>
-      <c r="D25" t="s">
-        <v>111</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920068</v>
-      </c>
-      <c r="B26" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" t="s">
-        <v>112</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920070</v>
-      </c>
-      <c r="B27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" t="s">
-        <v>113</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920070</v>
-      </c>
-      <c r="B28" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" t="s">
-        <v>93</v>
-      </c>
-      <c r="D28" t="s">
-        <v>113</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920386</v>
-      </c>
-      <c r="B29" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" t="s">
-        <v>114</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -4117,206 +3557,206 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920074</v>
+        <v>20330051920041</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920075</v>
+        <v>20330051920071</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920051</v>
+        <v>20330051920073</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920082</v>
+        <v>20330051920359</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920091</v>
+        <v>20330051920074</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920065</v>
+        <v>20330051920075</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920066</v>
+        <v>19330051920051</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920070</v>
+        <v>20330051920077</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920071</v>
+        <v>18330051920156</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920077</v>
+        <v>20330051920080</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920080</v>
+        <v>20330051920081</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920081</v>
+        <v>20330051920082</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -4324,16 +3764,16 @@
         <v>20330051920087</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4341,129 +3781,129 @@
         <v>20330051920090</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920093</v>
+        <v>20330051920091</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920059</v>
+        <v>20330051920093</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920061</v>
+        <v>20330051920059</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920064</v>
+        <v>20330051920061</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920068</v>
+        <v>20330051920062</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920386</v>
+        <v>20330051920063</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920041</v>
+        <v>20330051920064</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
         <v>123</v>
@@ -4474,13 +3914,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920073</v>
+        <v>20330051920065</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
         <v>124</v>
@@ -4491,13 +3931,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920359</v>
+        <v>20330051920066</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D24" t="s">
         <v>125</v>
@@ -4508,10 +3948,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>18330051920156</v>
+        <v>20330051920068</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
         <v>68</v>
@@ -4525,13 +3965,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920062</v>
+        <v>20330051920070</v>
       </c>
       <c r="B26" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s">
         <v>127</v>
@@ -4542,13 +3982,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920063</v>
+        <v>20330051920386</v>
       </c>
       <c r="B27" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s">
         <v>128</v>
@@ -4564,7 +4004,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4599,13 +4039,13 @@
         <v>20330051920073</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4622,13 +4062,13 @@
         <v>20330051920073</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4645,13 +4085,13 @@
         <v>20330051920082</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4660,7 +4100,7 @@
         <v>48</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4668,13 +4108,13 @@
         <v>20330051920082</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4683,27 +4123,27 @@
         <v>51</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920087</v>
+        <v>20330051920071</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4711,16 +4151,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920087</v>
+        <v>18330051920156</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4729,21 +4169,21 @@
         <v>48</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920093</v>
+        <v>20330051920080</v>
       </c>
       <c r="B8" t="s">
         <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4752,27 +4192,27 @@
         <v>48</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920093</v>
+        <v>20330051920087</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4780,39 +4220,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920071</v>
+        <v>20330051920093</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>18330051920156</v>
+        <v>20330051920063</v>
       </c>
       <c r="B11" t="s">
         <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4822,121 +4262,6 @@
       </c>
       <c r="G11">
         <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920080</v>
-      </c>
-      <c r="B12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>48</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920081</v>
-      </c>
-      <c r="B13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" t="s">
-        <v>101</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920063</v>
-      </c>
-      <c r="B14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C14" t="s">
-        <v>122</v>
-      </c>
-      <c r="D14" t="s">
-        <v>128</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920064</v>
-      </c>
-      <c r="B15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920068</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5AEV - Estadisticos 20221.xlsx
+++ b/grupos/5AEV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="129">
   <si>
     <t>Materia</t>
   </si>
@@ -960,7 +960,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -1049,7 +1049,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>-1</v>
@@ -1070,7 +1070,7 @@
         <v>5</v>
       </c>
       <c r="AA5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB5">
         <v>7</v>
@@ -1138,7 +1138,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1159,7 +1159,7 @@
         <v>5</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB6">
         <v>7</v>
@@ -1227,7 +1227,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -1316,7 +1316,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1494,7 +1494,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1515,7 +1515,7 @@
         <v>5</v>
       </c>
       <c r="AA10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB10">
         <v>5</v>
@@ -1672,7 +1672,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1693,7 +1693,7 @@
         <v>5</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB12">
         <v>9</v>
@@ -1761,7 +1761,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1850,7 +1850,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>-1</v>
@@ -1939,7 +1939,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -2028,7 +2028,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -2206,7 +2206,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2295,7 +2295,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>-1</v>
@@ -2316,7 +2316,7 @@
         <v>6</v>
       </c>
       <c r="AA19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB19">
         <v>8</v>
@@ -2473,7 +2473,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2562,7 +2562,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -2651,7 +2651,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
         <v>-1</v>
@@ -2740,7 +2740,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2761,7 +2761,7 @@
         <v>5</v>
       </c>
       <c r="AA24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB24">
         <v>6</v>
@@ -2829,7 +2829,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -3007,7 +3007,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -3096,7 +3096,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -3117,7 +3117,7 @@
         <v>5</v>
       </c>
       <c r="AA28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB28">
         <v>5</v>
@@ -3185,7 +3185,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>-1</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="AA29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB29">
         <v>7</v>
@@ -3405,16 +3405,16 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>65.38</v>
+        <v>80.77</v>
       </c>
       <c r="G6">
-        <v>34.62</v>
+        <v>19.23</v>
       </c>
       <c r="H6">
         <v>7.2</v>
@@ -4004,7 +4004,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4082,16 +4082,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920082</v>
+        <v>19330051920051</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4105,16 +4105,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920082</v>
+        <v>19330051920051</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4128,16 +4128,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920071</v>
+        <v>20330051920082</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4151,22 +4151,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>18330051920156</v>
+        <v>20330051920082</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4174,16 +4174,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920080</v>
+        <v>20330051920071</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920087</v>
+        <v>18330051920156</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4220,22 +4220,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920093</v>
+        <v>20330051920080</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4243,24 +4243,47 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
+        <v>20330051920087</v>
+      </c>
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
         <v>20330051920063</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>76</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>97</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>122</v>
       </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
         <v>48</v>
       </c>
-      <c r="G11">
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEV - Estadisticos 20221.xlsx
+++ b/grupos/5AEV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="129">
   <si>
     <t>Materia</t>
   </si>
@@ -957,7 +957,7 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -1046,7 +1046,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T5">
         <v>5</v>
@@ -1135,7 +1135,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>6</v>
@@ -1224,7 +1224,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1313,7 +1313,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T8">
         <v>5</v>
@@ -1402,7 +1402,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1491,7 +1491,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -1580,7 +1580,7 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -1669,7 +1669,7 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T12">
         <v>6</v>
@@ -1758,7 +1758,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -1847,7 +1847,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1868,7 +1868,7 @@
         <v>9</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>10</v>
@@ -1936,7 +1936,7 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -2025,7 +2025,7 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -2114,7 +2114,7 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -2203,7 +2203,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -2292,7 +2292,7 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>8</v>
@@ -2313,7 +2313,7 @@
         <v>6</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA19">
         <v>6</v>
@@ -2381,7 +2381,7 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2470,7 +2470,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>5</v>
@@ -2559,7 +2559,7 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2580,7 +2580,7 @@
         <v>9</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -2648,7 +2648,7 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -2737,7 +2737,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>6</v>
@@ -2758,7 +2758,7 @@
         <v>7</v>
       </c>
       <c r="Z24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>8</v>
@@ -2826,7 +2826,7 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2915,7 +2915,7 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T26">
         <v>-1</v>
@@ -3004,7 +3004,7 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -3025,7 +3025,7 @@
         <v>8</v>
       </c>
       <c r="Z27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA27">
         <v>8</v>
@@ -3093,7 +3093,7 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -3182,7 +3182,7 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T29">
         <v>8</v>
@@ -3277,19 +3277,19 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>30.77</v>
+        <v>34.62</v>
       </c>
       <c r="G2">
-        <v>69.23</v>
+        <v>65.38</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4004,7 +4004,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4264,29 +4264,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920063</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" t="s">
-        <v>122</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>48</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/5AEV - Estadisticos 20221.xlsx
+++ b/grupos/5AEV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="129">
   <si>
     <t>Materia</t>
   </si>
@@ -167,19 +167,19 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
     <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
     <t>Molina Quezada Raúl</t>
@@ -954,7 +954,7 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
         <v>8</v>
@@ -963,10 +963,10 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -1043,7 +1043,7 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
         <v>4</v>
@@ -1052,10 +1052,10 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -1073,10 +1073,10 @@
         <v>6</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1132,7 +1132,7 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6">
         <v>7</v>
@@ -1141,10 +1141,10 @@
         <v>6</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1221,7 +1221,7 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
         <v>8</v>
@@ -1230,10 +1230,10 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1242,7 +1242,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z7">
         <v>8</v>
@@ -1310,7 +1310,7 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
         <v>4</v>
@@ -1319,10 +1319,10 @@
         <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -1343,7 +1343,7 @@
         <v>5</v>
       </c>
       <c r="AC8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1399,19 +1399,19 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
         <v>4</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1420,13 +1420,13 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z9">
         <v>5</v>
       </c>
       <c r="AA9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB9">
         <v>5</v>
@@ -1488,7 +1488,7 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
         <v>7</v>
@@ -1497,10 +1497,10 @@
         <v>7</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1509,7 +1509,7 @@
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z10">
         <v>5</v>
@@ -1518,7 +1518,7 @@
         <v>6</v>
       </c>
       <c r="AB10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -1577,19 +1577,19 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S11">
         <v>4</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1598,19 +1598,19 @@
         <v>5</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z11">
         <v>5</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB11">
         <v>6</v>
       </c>
       <c r="AC11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1666,7 +1666,7 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
         <v>4</v>
@@ -1675,10 +1675,10 @@
         <v>6</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1687,7 +1687,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z12">
         <v>5</v>
@@ -1699,7 +1699,7 @@
         <v>9</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1755,7 +1755,7 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>5</v>
@@ -1764,10 +1764,10 @@
         <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1776,7 +1776,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z13">
         <v>5</v>
@@ -1785,7 +1785,7 @@
         <v>7</v>
       </c>
       <c r="AB13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC13">
         <v>8</v>
@@ -1844,7 +1844,7 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>8</v>
@@ -1853,10 +1853,10 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1865,7 +1865,7 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z14">
         <v>7</v>
@@ -1874,7 +1874,7 @@
         <v>10</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -1933,7 +1933,7 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
         <v>5</v>
@@ -1942,10 +1942,10 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1954,7 +1954,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z15">
         <v>5</v>
@@ -1963,7 +1963,7 @@
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC15">
         <v>7</v>
@@ -2022,7 +2022,7 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
         <v>7</v>
@@ -2031,10 +2031,10 @@
         <v>9</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -2043,7 +2043,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>6</v>
@@ -2055,7 +2055,7 @@
         <v>6</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2111,19 +2111,19 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
         <v>4</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -2144,7 +2144,7 @@
         <v>6</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2200,7 +2200,7 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
         <v>4</v>
@@ -2209,10 +2209,10 @@
         <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>6</v>
@@ -2230,7 +2230,7 @@
         <v>7</v>
       </c>
       <c r="AB18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC18">
         <v>7</v>
@@ -2289,7 +2289,7 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>8</v>
@@ -2298,10 +2298,10 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>10</v>
@@ -2378,19 +2378,19 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
         <v>4</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2408,7 +2408,7 @@
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC20">
         <v>7</v>
@@ -2467,7 +2467,7 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>7</v>
@@ -2476,10 +2476,10 @@
         <v>5</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2500,7 +2500,7 @@
         <v>7</v>
       </c>
       <c r="AC21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2556,7 +2556,7 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>10</v>
@@ -2565,10 +2565,10 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>9</v>
@@ -2645,7 +2645,7 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>10</v>
@@ -2654,10 +2654,10 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2734,7 +2734,7 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
         <v>7</v>
@@ -2743,10 +2743,10 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2823,7 +2823,7 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S25">
         <v>4</v>
@@ -2832,10 +2832,10 @@
         <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>6</v>
@@ -2853,7 +2853,7 @@
         <v>6</v>
       </c>
       <c r="AB25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC25">
         <v>7</v>
@@ -2912,19 +2912,19 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S26">
         <v>4</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>6</v>
@@ -2942,10 +2942,10 @@
         <v>5</v>
       </c>
       <c r="AB26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC26">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -3001,7 +3001,7 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
         <v>9</v>
@@ -3010,10 +3010,10 @@
         <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -3090,7 +3090,7 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
         <v>4</v>
@@ -3099,10 +3099,10 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -3120,10 +3120,10 @@
         <v>6</v>
       </c>
       <c r="AB28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3179,7 +3179,7 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S29">
         <v>4</v>
@@ -3188,10 +3188,10 @@
         <v>8</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -3309,19 +3309,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>61.54</v>
+        <v>42.31</v>
       </c>
       <c r="G3">
-        <v>38.46</v>
+        <v>57.69</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
@@ -3353,7 +3353,7 @@
         <v>38.46</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3364,7 +3364,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
@@ -3373,19 +3373,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>65.38</v>
+        <v>76.92</v>
       </c>
       <c r="G5">
-        <v>34.62</v>
+        <v>23.08</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3396,7 +3396,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
@@ -3417,7 +3417,7 @@
         <v>19.23</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3428,7 +3428,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
@@ -3437,19 +3437,19 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>84.62</v>
+        <v>92.31</v>
       </c>
       <c r="G7">
-        <v>15.38</v>
+        <v>7.69</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4004,7 +4004,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4036,22 +4036,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920073</v>
+        <v>20330051920071</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4059,22 +4059,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920073</v>
+        <v>20330051920071</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4082,22 +4082,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920051</v>
+        <v>20330051920073</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4105,22 +4105,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920051</v>
+        <v>20330051920073</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4128,22 +4128,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920082</v>
+        <v>19330051920051</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4151,22 +4151,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920082</v>
+        <v>19330051920051</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4174,22 +4174,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920071</v>
+        <v>20330051920080</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4197,16 +4197,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>18330051920156</v>
+        <v>20330051920080</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4220,22 +4220,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920080</v>
+        <v>20330051920082</v>
       </c>
       <c r="B10" t="s">
         <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4243,24 +4243,116 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
+        <v>20330051920082</v>
+      </c>
+      <c r="B11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920070</v>
+      </c>
+      <c r="B12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920070</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>18330051920156</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
         <v>20330051920087</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B15" t="s">
         <v>69</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C15" t="s">
         <v>91</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D15" t="s">
         <v>115</v>
       </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11">
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEV - Estadisticos 20221.xlsx
+++ b/grupos/5AEV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="129">
   <si>
     <t>Materia</t>
   </si>
@@ -948,10 +948,10 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
         <v>9</v>
@@ -969,10 +969,10 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -1037,10 +1037,10 @@
         <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
         <v>8</v>
@@ -1058,10 +1058,10 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -1126,10 +1126,10 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
         <v>5</v>
@@ -1215,10 +1215,10 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
         <v>9</v>
@@ -1239,7 +1239,7 @@
         <v>10</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1304,10 +1304,10 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
         <v>5</v>
@@ -1325,7 +1325,7 @@
         <v>5</v>
       </c>
       <c r="W8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>5</v>
@@ -1393,10 +1393,10 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <v>5</v>
@@ -1414,7 +1414,7 @@
         <v>5</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1482,10 +1482,10 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
         <v>8</v>
@@ -1571,10 +1571,10 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
         <v>5</v>
@@ -1592,7 +1592,7 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>5</v>
@@ -1660,10 +1660,10 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
         <v>5</v>
@@ -1681,10 +1681,10 @@
         <v>4</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1749,10 +1749,10 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>8</v>
@@ -1770,7 +1770,7 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -1838,10 +1838,10 @@
         <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
         <v>8</v>
@@ -1927,10 +1927,10 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R15">
         <v>7</v>
@@ -1948,10 +1948,10 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -2016,10 +2016,10 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
         <v>5</v>
@@ -2037,10 +2037,10 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -2105,10 +2105,10 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
         <v>5</v>
@@ -2126,7 +2126,7 @@
         <v>2</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -2194,10 +2194,10 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
         <v>7</v>
@@ -2215,10 +2215,10 @@
         <v>6</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2283,10 +2283,10 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>7</v>
@@ -2372,10 +2372,10 @@
         <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
         <v>5</v>
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
         <v>8</v>
@@ -2482,7 +2482,7 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>5</v>
@@ -2550,10 +2550,10 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
         <v>9</v>
@@ -2639,10 +2639,10 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
         <v>10</v>
@@ -2663,7 +2663,7 @@
         <v>10</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>10</v>
@@ -2728,10 +2728,10 @@
         <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
         <v>8</v>
@@ -2817,10 +2817,10 @@
         <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R25">
         <v>5</v>
@@ -2838,7 +2838,7 @@
         <v>7</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>5</v>
@@ -2906,10 +2906,10 @@
         <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
         <v>5</v>
@@ -2995,10 +2995,10 @@
         <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>9</v>
@@ -3084,10 +3084,10 @@
         <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
         <v>5</v>
@@ -3108,7 +3108,7 @@
         <v>7</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>5</v>
@@ -3173,10 +3173,10 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R29">
         <v>5</v>
@@ -3341,19 +3341,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>61.54</v>
+        <v>69.23</v>
       </c>
       <c r="G4">
-        <v>38.46</v>
+        <v>30.77</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3469,19 +3469,19 @@
         <v>26</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>96.15000000000001</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4004,7 +4004,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4266,16 +4266,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920070</v>
+        <v>20330051920091</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -4289,16 +4289,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920070</v>
+        <v>20330051920091</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4312,22 +4312,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>18330051920156</v>
+        <v>20330051920070</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -4335,24 +4335,47 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920087</v>
+        <v>20330051920070</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>18330051920156</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16">
         <v>5</v>
       </c>
     </row>
